--- a/Planos.xlsx
+++ b/Planos.xlsx
@@ -56,9 +56,6 @@
     <t>Empresa</t>
   </si>
   <si>
-    <t>Até 30 piscinas</t>
-  </si>
-  <si>
     <t>R$ 29,90/mês</t>
   </si>
   <si>
@@ -69,6 +66,9 @@
   </si>
   <si>
     <t>R$ 209,90/mês</t>
+  </si>
+  <si>
+    <t>acima de 10 piscinas</t>
   </si>
 </sst>
 </file>
@@ -430,7 +430,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -441,7 +441,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -452,7 +452,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -460,10 +460,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
